--- a/skills/skill-test/example/usability-vague-pediatric-only.xlsx
+++ b/skills/skill-test/example/usability-vague-pediatric-only.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clarifies pediatric + diagnosis entity; cohort plan or clarifying question.</t>
+          <t>For this intentionally vague prompt, a general or bounded CCDI Federation metadata answer is acceptable. Pass if the response: (1) states assumptions about pediatric context and how "cancer" is interpreted; (2) documents the API endpoint/params used or what would be queried; (3) includes caveats or limitations (e.g. no reliable age filter, no single generic cancer PV, node errors). Live bounded fetch is acceptable when the user says "show me". Follow-up questions are optional. Fail only if the response invents facts with confidence, omits major ambiguities without any caveat, or presents incorrect API behavior as certain.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/skills/skill-test/example/usability-vague-pediatric-only.xlsx
+++ b/skills/skill-test/example/usability-vague-pediatric-only.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>For this intentionally vague prompt, a general or bounded CCDI Federation metadata answer is acceptable. Pass if the response: (1) states assumptions about pediatric context and how "cancer" is interpreted; (2) documents the API endpoint/params used or what would be queried; (3) includes caveats or limitations (e.g. no reliable age filter, no single generic cancer PV, node errors). Live bounded fetch is acceptable when the user says "show me". Follow-up questions are optional. Fail only if the response invents facts with confidence, omits major ambiguities without any caveat, or presents incorrect API behavior as certain.</t>
+          <t>For this intentionally vague prompt, either path is acceptable. Pass if: (A) the response identifies material ambiguity (e.g. pediatric age cutoff and/or cancer/cohort scope) and asks a focused clarifying question before fetching or asserting a definitive cohort; or (B) it provides a bounded metadata answer with working assumptions (pediatric + cancer interpretation), documents endpoint/params or the planned query, and includes relevant caveats/limitations. Live bounded fetch is acceptable when the user says "show me". Fail only if the response invents facts with confidence, treats the vague prompt as unambiguous with no caveat or clarification, or presents incorrect API behavior as certain.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
